--- a/docs/bug-feature-list.xlsx
+++ b/docs/bug-feature-list.xlsx
@@ -2,16 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bug清单" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求清单" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -21,10 +16,8 @@
   <fonts count="2">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
@@ -39,13 +32,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -55,9 +42,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -172,72 +158,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -293,7 +221,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -302,13 +230,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -342,17 +270,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -407,8 +324,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -418,7 +333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -509,8 +424,89 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>无法访问简历编辑器 Web 页面</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>用户反馈无法访问简历编辑器 Web 页面。根因是前端 5173 与 API 3001 服务均未启动；现已启动并验证首页 HTTP 200、API 健康检查正常、前端代理链路正常。</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>已修复</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>B-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>简历编辑器 Web 页面再次无法访问</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>用户反馈简历编辑器 Web 页面再次无法访问。根因是前端 5173 与 API 3001 服务均未运行；已重新启动并验证首页 HTTP 200、API 健康检查正常、前端代理链路正常。</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>已修复</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>B-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PDF/HTML 导出按钮重复显示</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>简历编辑器顶栏与预览工具栏重复渲染 PDF/HTML 导出入口。现已按用户确认将 PDF、HTML、JSON 导出统一放入预览区，顶栏不再显示导出按钮。</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>已修复</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -520,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -665,7 +661,331 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>简历编辑器 UI 优化</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>优化编辑器的信息层级、操作反馈与三栏布局，使模块管理、子项调整和实时预览更清晰易用。</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>简历子项按版本隐藏与恢复</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>模块展开后可对项目、经历等子项执行隐藏/恢复；仅影响当前简历的预览与最终导出，不删除 Wiki 源数据。</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>简历预览与导出版式优化</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>调研优秀简历排版，优化字体、间距、信息层级、时间与正文布局，并确保预览、HTML 与 PDF 输出一致。</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>深化简历编辑器 UI</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>基于 ui-ux-pro-max 优化视觉层级、图标一致性、操作热区、键盘可用性、响应式布局与状态反馈。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Career-Wiki-Skill 米白极简 UI 优化</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>去掉 AI 感，整体 Web UI 调整为米白色极简风，并优化字体与信息层级。对应任务板 LOCAL-2。</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>预览区联系方式添加 SVG 图标</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>点击预览区的导出 PDF 后，使用 html2pdf.js 将当前 A4 预览直接生成并下载为 PDF 文件，不再调用浏览器打印对话框或要求选择打印机。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-010</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PDF 导出改为直接下载</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>点击导出 PDF 后应直接下载渲染好的 PDF 文件，不再调用浏览器打印对话框或要求选择打印机。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>待开发</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-011</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Wiki 图谱字体颜色可读性优化</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>已提高 Wiki 图谱节点标签、关系标签、图例、顶部统计和详情侧栏文字的颜色对比度；实体徽章前景色自动适配背景，并通过 WCAG AA 对比度测试。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-012</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>项目详情新增岗位职责字段</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>项目详情保留独立的 description 与 responsibilities 字段；编辑区 responsibilities 紧跟 description；预览分别显示“项目描述：&lt;description&gt;”和“岗位职责：&lt;responsibilities&gt;”，禁止混合字段内容。</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F-013</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>项目详情新增技术栈字段</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>项目详情新增独立的 tech_stack 字段，用于存放该项目使用到的技术栈；不得混入 description 或 responsibilities，并在编辑区和预览区独立展示。</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F-014</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>项目采访补充深度信息并存档知识库</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>项目采访必须询问项目描述、本人职责、技术栈、遇到的困难及解决方案，并保留相关原始回答；Wiki 项目实体分别存储这些信息，其中困难与解决方案默认不进入简历模板。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>F-015</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>项目采访补问改为逐题确认</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>项目采访补问遗漏项时一次只问一个问题；等待用户回答后再继续。若当前回答不明确，围绕当前问题追问并确认，只有明确后才能进入下一问题，禁止一次抛出多个问题。</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/bug-feature-list.xlsx
+++ b/docs/bug-feature-list.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -985,6 +985,33 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>F-016</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>同步 README 并发布 GitHub</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>README 同步本轮新增能力：简历编辑器 UI、直接 PDF 下载、Wiki 图谱可读性、项目独立字段与深度串行采访；完成后提交并推送到 GitHub。</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/bug-feature-list.xlsx
+++ b/docs/bug-feature-list.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1012,6 +1012,33 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>F-017</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>远程仓库排除 .wayfinder 目录</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>将 .wayfinder/ 加入 .gitignore；若目录已被 Git 跟踪，则仅从索引和后续远程版本中移除，保留本地文件。</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/bug-feature-list.xlsx
+++ b/docs/bug-feature-list.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>已完成</t>
         </is>
       </c>
     </row>
